--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-25 14:51 from tracking/tasks.json</t>
+          <t>Generated 2026-10-25 19:29 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -886,30 +886,58 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11 Tenant management</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="n">
+      <c r="B18" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -924,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5245,9 +5273,209 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>T162</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>11 Tenant management</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Add tenants: tenant.create permission, checked wrappers over owner-run installers, Tenants screen with session refresh</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Request 2026-10-25</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>config.uspCreateRoot/ChildTenant, /admin/tenants</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>Platform admin anywhere; region admin states/tribes under region; Administrator role programs/jurisdictions; user administrator refused. Unit, scenario and e2e tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>T163</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>11 Tenant management</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Reporter registry: laboratories, facilities, providers; one-entry add/correct; checked CSV import of NPI and CLIA records</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Request 2026-10-25</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>/reporters, dbo.uspListReporters, dbo.uspImportReporters</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>registry.edit for intake clerk, supervisor, administrator; sample samples/registry_npi_clia_sample.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>T164</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>11 Tenant management</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Extracts: View findings dialog and Mark submitted; quarter label fix and default to the last completed quarter</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Request 2026-10-25</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>/extracts, dbo.uspMarkExtractSubmitted</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>extract.submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>T165</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>11 Tenant management</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>User guides: Daily Operations and Importing NPI and CLIA Records (PDF), three Archify workflow diagrams, access guide and README updates</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Request 2026-10-25</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>Real screenshots in docs/images/guide; sources in docs/guides</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
-  <conditionalFormatting sqref="F2:F94">
+  <autoFilter ref="A1:J98"/>
+  <conditionalFormatting sqref="F2:F98">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-25 19:29 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 13:24 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -914,30 +914,58 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="n">
+      <c r="B19" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5" t="n">
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -952,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5473,9 +5501,109 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>T166</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Retake the user guide screenshots after the #3 fixes; print every image at one scale with whole-element crops; add the capture, sizing and print tools</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Request 2026-10-26</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>docs/guides, docs/images/guide</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>PR #5; Daily Operations 26 pages, NPI/CLIA 8 pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T167</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Code review of sourceCode: verify findings and log them as GitHub issues with recommendations</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Request 2026-10-26</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issues #6-#21</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>16 issues: 3 security (#6 county mapping, #7 job session scope, #8 sign-in rate limit), 8 bugs, 1 performance, 4 UI/maintainability</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
-  <conditionalFormatting sqref="F2:F98">
+  <autoFilter ref="A1:J100"/>
+  <conditionalFormatting sqref="F2:F100">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 13:24 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 13:44 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5601,9 +5601,59 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>T168</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Issue #6: below the data root a new tenant serves only its parent's counties; new counties only under the root (enforced in config.uspInstallChildTenant for every caller)</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #6</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>procs_setup.py, Tenants screen, AuthorizationScenarioTests</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>Scenario test BelowTheDataRootANewTenantServesOnlyItsParentsCounties; form lists only the parent's counties</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
-  <conditionalFormatting sqref="F2:F100">
+  <autoFilter ref="A1:J101"/>
+  <conditionalFormatting sqref="F2:F101">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 13:44 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 14:11 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5651,9 +5651,59 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>T169</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Issue #7: background jobs run under the queuing session's profile, view-as and acting tenant (stored on dbo.jobQueue; JobSessions.OpenAsync)</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #7</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>jobQueue, enqueue procedures, JobWorker, JobSessions</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>Scenario test ABackgroundJobKeepsTheProfileAndTenantOfTheSessionThatQueuedIt; JobSessionTests</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
-  <conditionalFormatting sqref="F2:F101">
+  <autoFilter ref="A1:J102"/>
+  <conditionalFormatting sqref="F2:F102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 14:11 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 14:24 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5701,9 +5701,59 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>T170</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Issue #8: sign-in rate limits per client address (sliding window; password and code steps counted separately), Too many attempts page with Retry-After, configurable limits, trusted reverse proxies for X-Forwarded-For</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #8</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>sourceCode/src/Merit.Web/Infrastructure/SignInRateLimits.cs</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>SignInRateLimitTests: one client over the limit does not hold up another; rejected forms count</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
-  <conditionalFormatting sqref="F2:F102">
+  <autoFilter ref="A1:J103"/>
+  <conditionalFormatting sqref="F2:F103">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 14:24 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 14:42 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5751,9 +5751,59 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>T171</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Issue #14: intake registry lookups by index seek and once per batch: identifier-first filtered indexes on organization CLIA/NPI and provider NPI, uspResolveOrganization and uspImportReporters try CLIA then NPI then name, new uspGetProviderByNpi, RegistryLookups cache in IntakeProcessor</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #14</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>organization, provider, uspResolveOrganization, uspImportReporters, uspGetProviderByNpi, RegistryLookups</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>RegistryLookupTests; scenario test RegistryLookupsTryTheCliaNumberThenTheNpiThenTheName; 100k-row check: 8,694 to 6 logical reads (CLIA), 8,155 to 3 (NPI)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
-  <conditionalFormatting sqref="F2:F103">
+  <autoFilter ref="A1:J104"/>
+  <conditionalFormatting sqref="F2:F104">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 14:42 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 18:18 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5801,9 +5801,59 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>T172</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Issue #9: a chosen held group lists only its own rows: uspListHeldRows takes the sender and an exact-group flag (null value or sender means none), held groups carry the sender's id, the held page asks for the exact group and shows it above the grid</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #9</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>uspListHeldRows, IntakeService.HeldRowsAsync, api/v1/held/rows, held.page.ts</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>HeldRecordsTests: two senders sharing a cause and value; follow-up issue #29 (uspCreateWorkTask cross-tenant references) found on the way</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
-  <conditionalFormatting sqref="F2:F104">
+  <autoFilter ref="A1:J105"/>
+  <conditionalFormatting sqref="F2:F105">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 18:18 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 18:33 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5851,9 +5851,59 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>T173</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Issue #29: uspCreateWorkTask refuses links to records the caller cannot see (51404); the cross-tenant suite aims at real records only (seeded staging row and cluster, no random-id fallback) and checks every write for hidden ids stored in the caller's own rows</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #29</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>uspCreateWorkTask, CrossTenantTests.cs</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>ATaskCanLinkOnlyRecordsTheCallerCanSee; the suite reproduced the gap on every run before the fix</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
-  <conditionalFormatting sqref="F2:F105">
+  <autoFilter ref="A1:J106"/>
+  <conditionalFormatting sqref="F2:F106">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 18:33 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 19:26 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5901,9 +5901,259 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>T174</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Issue #12: one NPI and CLIA normalization (spaces and hyphens removed, CLIA upper case) shared by the registry and intake</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #12</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>ProviderIdentifiers, RegistryService, IntakeProcessor</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>ProviderIdentifierTests</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>T175</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Issue #11: one organization per CLIA number and per NPI: file check by identifier whatever the type, import groups shared identifiers into one organization, uspSaveOrganization refuses duplicates, unique indexes (generateTables dropIndexes)</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #11</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>RegistryService.CheckFile, uspImportReporters, uspSaveOrganization, dbo.organization</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>RegistryCheckTests; OneImportMakesOneOrganizationPerIdentifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>T176</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Issue #10: held-row corrections merge as a patch on the server; the page sends only changed fields and refreshes the open row</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #10</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>uspSaveStagingCorrection, held.page.ts</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>HeldRecordsTests.ASecondCorrectionKeepsTheFirst</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>T177</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Issue #15: Reporters filter is a plain text input (role searchbox), USWDS search-box override removed</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #15</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Views/Reporters/Index.cshtml, merit.css</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>e2e layout.spec.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>T178</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Issue #16: batch card file names break after underscores, dots and hyphens; card headings wrap anywhere as a last resort</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #16</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Views/Intake/_Batches.cshtml, merit.css</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>e2e layout.spec.ts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
-  <conditionalFormatting sqref="F2:F106">
+  <autoFilter ref="A1:J111"/>
+  <conditionalFormatting sqref="F2:F111">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 19:26 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 19:45 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6151,9 +6151,209 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>T179</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>Issue #13: Case timeliness report counts only follow-up activity types and reports cases not followed up yet</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #13</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>uspReportCaseTimeliness, ReviewServices</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J112" s="7" t="inlineStr">
+        <is>
+          <t>CaseTimelinessCountsOnlyFollowUpWork</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>T180</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Issue #19: Search results show open cases as linked case chips (shared _CaseChip partial with the person header); uspSearch returns them as JSON</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #19</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>uspSearch, Views/Search/_Results.cshtml, Views/Shared/_CaseChip.cshtml</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>EndpointTests.SearchShowsOpenCasesAsChipsLinkingToTheCase</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>T181</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Issue #17: Extract run card actions in their own row; Download label breaks file names after underscores (FileNames.Breakable)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #17</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Views/Extracts/_Runs.cshtml, merit.css, FileNames.cs</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>e2e layout.spec.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>T182</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Issue #18: Row and grid forms no longer capped at 20rem; Reporters add form in columns, showing only the chosen kind's fields</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #18</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>merit.css, Views/Reporters/Index.cshtml</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>e2e layout.spec.ts</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J111"/>
-  <conditionalFormatting sqref="F2:F111">
+  <autoFilter ref="A1:J115"/>
+  <conditionalFormatting sqref="F2:F115">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 19:45 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 20:21 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6351,9 +6351,159 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>T183</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Issue #20: intake refuses a file already received for the same profile (contentSha256 on intakeBatch, uspFindIntakeBatchByContent) unless marked as a genuine re-send; 20 MB limit measured in bytes</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #20</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>intakeBatch, uspCreateIntakeBatch, IntakeService, Intake page</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>IntakeUploadTests</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>T184</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Issue #21: one SessionRenewal for sign-in, profile, view-as and tenant refresh; Session:LifetimeHours; ProfileId and ViewAsUserId on ICurrentSession</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #21</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>SessionRenewal.cs, Account/Profiles/Tenants controllers</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>EndpointTests.ASessionRenewalReplacesTheScopeWithTheConfiguredLifetime</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>T185</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Guide screenshots retaken on a fresh MERIT_GUIDES demo, guide text updated for #10-#13, #18-#20, Daily Operations and NPI/CLIA PDFs reprinted; card lists keep their width</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>User guides</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>docs/guides, docs/images/guide, merit.css</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t>Capture recipe in docs/guides/README.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J115"/>
-  <conditionalFormatting sqref="F2:F115">
+  <autoFilter ref="A1:J118"/>
+  <conditionalFormatting sqref="F2:F118">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 20:21 from tracking/tasks.json</t>
+          <t>Generated 2026-10-26 20:32 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6501,9 +6501,59 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>T186</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Issue #26: intake profile picker shows the version number (explicit Razor expression); the page render test fails on any unrendered Razor</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issue #26</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Views/Intake/Index.cshtml, EndpointTests</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>Check flags /intake on the old view and no other page</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
-  <conditionalFormatting sqref="F2:F118">
+  <autoFilter ref="A1:J119"/>
+  <conditionalFormatting sqref="F2:F119">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 20:32 from tracking/tasks.json</t>
+          <t>Generated 2026-10-27 05:51 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6551,9 +6551,459 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>T187</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>UX review of the running application (34 screens at 1280 and 390 px, three roles, forms, errors, axe): 16 issues filed, #36 to #51</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>GitHub issues #36-#51</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Issues labelled ux; screenshots on the issue-assets branch (ux_review/)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>axe: no violations at 1280 px; main findings: UTC dates, raw codes, phone layout, first sign-in not recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>T188</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Dates and "today" in the jurisdiction's time zone, not UTC</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Issue #36</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>auth.tenant.timeZone; JurisdictionClock (IClock); auth.udfSessionToday; session claim merit:tz; DisplayTime; /api/v1/me timeZone</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>Tenant form picks the zone; SQL today via session context; default Eastern</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>T189</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Codes and file fields shown as words on the result pages and the Angular client</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Issues #37, #38</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>DisplayNames; GET /api/v1/reference/labels; Angular Display service; Results/Details field labels</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>Lookup display names, analytes, system codes and staging field labels in one place</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T190</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>One date format in the Angular client; case numbers and dates stay on one line</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Issue #39</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Display.date/dateOf/month; GridColumn.nowrap; merit-nowrap in Razor lists</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>e2e: no line breaks inside case numbers or dates, no ISO dates in the queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T191</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Home names each urgent held record and links to its batch</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Issue #40</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>uspGetDashboard held rows; Home view; IntakeProcessor message</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>Title is person and analyte with value; "Held at intake from &lt;sender&gt;"</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T192</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Queue bulk assign waits for a chosen person and names them</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Issue #41</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>features/queues/queues.page.ts</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>List starts on "Choose a person..."; Assign disabled until chosen; message names the assignee</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>T193</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Unknown addresses and other status codes show a MERIT page</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Issue #43</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>HomeController.Status; UseStatusCodePagesWithReExecute outside /api</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>404, 403, 405/415 and 5xx pages; all methods, no antiforgery on the status page</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>T194</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>First sign-in after enrolment is recorded</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Issue #44</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>AccountService.CompleteEnrollmentAsync; Users page shows Never</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>Integration test FirstSignInTests</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T195</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Phone width: Menu button, usable search, no sideways scroll</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Issue #47</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>_Layout header; merit.css; merit.js; queues, reports and cluster layouts</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>e2e at 390 px: header folds, no main page wider than the screen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J119"/>
-  <conditionalFormatting sqref="F2:F119">
+  <autoFilter ref="A1:J128"/>
+  <conditionalFormatting sqref="F2:F128">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 05:51 from tracking/tasks.json</t>
+          <t>Generated 2026-10-27 08:42 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7001,9 +7001,159 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T196</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Required fields marked; server errors shown as a USWDS error summary on Add a person and Enter a result</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Issue #46</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>FormErrors; _ErrorSummary; _PersonForm; _ResultForm; _ResultFields; _Combobox; merit.js</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>Forms novalidate; summary in form order, linked and focused; result page post kept its errors; nonce bug found and logged as #53</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T197</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Focus ring hidden on script-focused headings for mouse users</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Issue #51</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>merit.css [tabindex=-1]:focus:not(:focus-visible)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>Keyboard focus keeps the ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T198</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Timeline axis labelled by span: years, months or days; no two-digit year</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Issue #49</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>features/timeline/timeline.page.ts axisTicks</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>e2e checks label shape against the visible range</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J128"/>
-  <conditionalFormatting sqref="F2:F128">
+  <autoFilter ref="A1:J131"/>
+  <conditionalFormatting sqref="F2:F131">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 08:42 from tracking/tasks.json</t>
+          <t>Generated 2026-10-27 09:13 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7151,9 +7151,59 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T199</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>CSP nonce in base64url, so htmx partials keep their htmx attributes</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Issue #53</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Infrastructure/Htmx.cs CspNonce</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>A '+' was HTML-encoded in hx-nonce and hx-csp stripped about one partial in three; unit and integration tests added</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
-  <conditionalFormatting sqref="F2:F131">
+  <autoFilter ref="A1:J132"/>
+  <conditionalFormatting sqref="F2:F132">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 09:13 from tracking/tasks.json</t>
+          <t>Generated 2026-10-27 13:40 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7201,9 +7201,109 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T200</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Held rows held for an uncertain match link to Match review; Release skips them</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Issue #42</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>HeldRowDto.ReasonCodes; features/held; features/match-review ?row=</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>Release disabled with an explanation when only such rows are selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T201</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Audit log: filters, paging, words, record links, CSV export</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Issue #45</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>logs.uspSearchAuditEvents; logs.uspListAuditUsers; AuditText; Views/Admin/Audit; _AuditLink</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>Filters by user, action, record type, dates, record; 100 a page; export audited; links from person, case and result pages</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
-  <conditionalFormatting sqref="F2:F132">
+  <autoFilter ref="A1:J134"/>
+  <conditionalFormatting sqref="F2:F134">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 13:40 from tracking/tasks.json</t>
+          <t>Generated 2026-10-27 15:34 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7301,9 +7301,59 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T202</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Case and cluster maps: county outlines for context, a 320 px cluster map, linked cluster tasks</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Issue #48</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>config.subJurisdiction boundary; uspSetSubJurisdictionBoundary; uspListSubJurisdictionBoundaries; tools/boundaries.py; shared/map</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>Outlines served by MERIT (no tile service); Maryland's from Census TIGERweb in the demo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J134"/>
-  <conditionalFormatting sqref="F2:F134">
+  <autoFilter ref="A1:J135"/>
+  <conditionalFormatting sqref="F2:F135">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>

--- a/tracking/MERIT_Task_Tracker.xlsx
+++ b/tracking/MERIT_Task_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$J$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 15:34 from tracking/tasks.json</t>
+          <t>Generated 2026-10-27 16:57 from tracking/tasks.json</t>
         </is>
       </c>
     </row>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7351,9 +7351,59 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T203</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>12 Quality</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Cases list: filters, search, sortable columns, one-click unassigned</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Issue #50</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>dbo.uspListExposureCases; dbo.uspListCaseOwners; Views/Cases/Index, _CaseList; CaseFilterModel</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>Assigned (me, nobody, a person), classification, population, analyte, owner, case number or last name; sort by case, person, classification, opened</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J135"/>
-  <conditionalFormatting sqref="F2:F135">
+  <autoFilter ref="A1:J136"/>
+  <conditionalFormatting sqref="F2:F136">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
